--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>C250106</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129867846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>C250106</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129867852</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,8 +1025,18 @@
           <t>C250106</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129868034</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129867846</v>
+        <v>136438458</v>
       </c>
       <c r="B2" t="n">
-        <v>58636</v>
+        <v>99245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stöpsjön, Filipstadsområdet, Vrm</t>
+          <t>Skåkstenen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442950</v>
+        <v>446412</v>
       </c>
       <c r="R2" t="n">
-        <v>6626425</v>
+        <v>6628537</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I ytterslänt på västra sidan vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,31 +779,31 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Lindkvist</t>
+          <t>Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>C250106</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129867846</t>
+          <t>https://artportalen.se/Sighting/136438458</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129867852</v>
+        <v>136438460</v>
       </c>
       <c r="B3" t="n">
-        <v>58636</v>
+        <v>99245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,46 +811,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stöpsjön, Filipstadsområdet, Vrm</t>
+          <t>Skåkstenen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442741</v>
+        <v>446421</v>
       </c>
       <c r="R3" t="n">
-        <v>6626344</v>
+        <v>6628526</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +874,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I ytterslänt på västra sidan vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,31 +899,31 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Lindkvist</t>
+          <t>Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>C250106</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129867852</t>
+          <t>https://artportalen.se/Sighting/136438460</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129868034</v>
+        <v>136438461</v>
       </c>
       <c r="B4" t="n">
-        <v>57602</v>
+        <v>99245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,49 +931,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100063</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stöpsjön, Filipstadsområdet, Vrm</t>
+          <t>Skåkstenen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444161</v>
+        <v>446452</v>
       </c>
       <c r="R4" t="n">
-        <v>6626245</v>
+        <v>6628492</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,17 +994,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hördes locka på avstånd, först flygande och sen troligen att den gick ner. Ungefärlig plats</t>
+          <t>I ytterslänt på västra sidan vägen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,20 +1019,973 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Noah Wester, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136438461</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136438463</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99245</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skåkstenen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>446466</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6628492</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I ytterslänt på östra sidan vägen. 3 exemplar tätt växande</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Noah Wester, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136438463</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136438464</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99245</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skåkstenen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>446440</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6628525</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I ytterslänt på östra sidan vägen. 12 exemplar med varierande mellanrum. 7m från vardera sida om punkten.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Noah Wester, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136438464</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136438465</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99245</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skåkstenen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>446427</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6628541</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I ytterslänt på östra sidan vägen. 3 exemplar med 2 meter mellanrum</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Noah Wester, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136438465</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136438459</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99352</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skåkstenen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>446410</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6628535</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I ytterslänt på västra sidan vägen. Växer i grusig slänt.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Noah Wester, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136438459</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136438470</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99245</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>446723</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6628043</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I ytterslänt på norra sidan vägen.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Noah Wester, Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136438470</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129867846</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stöpsjön, Filipstadsområdet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>442950</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6626425</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Stefan Lindkvist</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Olle Kvarnbäck</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>C250106</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129867846</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129867852</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stöpsjön, Filipstadsområdet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>442741</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6626344</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stefan Lindkvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>C250106</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129867852</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129868034</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57602</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stöpsjön, Filipstadsområdet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>444161</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6626245</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Färnebo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hördes locka på avstånd, först flygande och sen troligen att den gick ner. Ungefärlig plats</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stefan Lindkvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>C250106</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129868034</t>
         </is>
@@ -1036,6 +1996,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438458</v>
       </c>
       <c r="B2" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438460</v>
       </c>
       <c r="B3" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438461</v>
       </c>
       <c r="B4" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438463</v>
       </c>
       <c r="B5" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438464</v>
       </c>
       <c r="B6" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136438465</v>
       </c>
       <c r="B7" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>136438459</v>
       </c>
       <c r="B8" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>136438470</v>
       </c>
       <c r="B9" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 3485-2022 artfynd.xlsx
+++ b/artfynd/S 3485-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438458</v>
       </c>
       <c r="B2" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438460</v>
       </c>
       <c r="B3" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438461</v>
       </c>
       <c r="B4" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438463</v>
       </c>
       <c r="B5" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438464</v>
       </c>
       <c r="B6" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136438465</v>
       </c>
       <c r="B7" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>136438459</v>
       </c>
       <c r="B8" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>136438470</v>
       </c>
       <c r="B9" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
